--- a/inst/extdata/community_excel.xlsx
+++ b/inst/extdata/community_excel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -430,6 +430,11 @@
           <t>Environment5</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>JobSatisfaction</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,9 @@
       <c r="O2">
         <v>4</v>
       </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -528,6 +536,9 @@
       <c r="O3">
         <v>4</v>
       </c>
+      <c r="P3">
+        <v>-98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,6 +588,9 @@
       <c r="O4">
         <v>4</v>
       </c>
+      <c r="P4">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,6 +640,9 @@
       <c r="O5">
         <v>1</v>
       </c>
+      <c r="P5">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -675,6 +692,9 @@
       <c r="O6">
         <v>4</v>
       </c>
+      <c r="P6">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -724,6 +744,9 @@
       <c r="O7">
         <v>5</v>
       </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -773,6 +796,9 @@
       <c r="O8">
         <v>1</v>
       </c>
+      <c r="P8">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -822,6 +848,9 @@
       <c r="O9">
         <v>5</v>
       </c>
+      <c r="P9">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -871,6 +900,9 @@
       <c r="O10">
         <v>5</v>
       </c>
+      <c r="P10">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -920,6 +952,9 @@
       <c r="O11">
         <v>1</v>
       </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -969,6 +1004,9 @@
       <c r="O12">
         <v>3</v>
       </c>
+      <c r="P12">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1018,6 +1056,9 @@
       <c r="O13">
         <v>5</v>
       </c>
+      <c r="P13">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1067,6 +1108,9 @@
       <c r="O14">
         <v>3</v>
       </c>
+      <c r="P14">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1116,6 +1160,9 @@
       <c r="O15">
         <v>3</v>
       </c>
+      <c r="P15">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1165,6 +1212,9 @@
       <c r="O16">
         <v>4</v>
       </c>
+      <c r="P16">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1214,6 +1264,9 @@
       <c r="O17">
         <v>5</v>
       </c>
+      <c r="P17">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1263,6 +1316,9 @@
       <c r="O18">
         <v>5</v>
       </c>
+      <c r="P18">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1312,6 +1368,9 @@
       <c r="O19">
         <v>2</v>
       </c>
+      <c r="P19">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1361,6 +1420,9 @@
       <c r="O20">
         <v>3</v>
       </c>
+      <c r="P20">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1410,6 +1472,9 @@
       <c r="O21">
         <v>1</v>
       </c>
+      <c r="P21">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1459,6 +1524,9 @@
       <c r="O22">
         <v>1</v>
       </c>
+      <c r="P22">
+        <v>-98</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1508,6 +1576,9 @@
       <c r="O23">
         <v>1</v>
       </c>
+      <c r="P23">
+        <v>5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1557,6 +1628,9 @@
       <c r="O24">
         <v>1</v>
       </c>
+      <c r="P24">
+        <v>-99</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1606,6 +1680,9 @@
       <c r="O25">
         <v>3</v>
       </c>
+      <c r="P25">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1655,6 +1732,9 @@
       <c r="O26">
         <v>1</v>
       </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1704,6 +1784,9 @@
       <c r="O27">
         <v>5</v>
       </c>
+      <c r="P27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1753,6 +1836,9 @@
       <c r="O28">
         <v>3</v>
       </c>
+      <c r="P28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1802,6 +1888,9 @@
       <c r="O29">
         <v>1</v>
       </c>
+      <c r="P29">
+        <v>9</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1851,6 +1940,9 @@
       <c r="O30">
         <v>1</v>
       </c>
+      <c r="P30">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1900,6 +1992,9 @@
       <c r="O31">
         <v>4</v>
       </c>
+      <c r="P31">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1949,6 +2044,9 @@
       <c r="O32">
         <v>2</v>
       </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1998,6 +2096,9 @@
       <c r="O33">
         <v>5</v>
       </c>
+      <c r="P33">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2047,6 +2148,9 @@
       <c r="O34">
         <v>4</v>
       </c>
+      <c r="P34">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2096,6 +2200,9 @@
       <c r="O35">
         <v>3</v>
       </c>
+      <c r="P35">
+        <v>-99</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2145,6 +2252,9 @@
       <c r="O36">
         <v>3</v>
       </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2194,6 +2304,9 @@
       <c r="O37">
         <v>3</v>
       </c>
+      <c r="P37">
+        <v>5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2243,6 +2356,9 @@
       <c r="O38">
         <v>5</v>
       </c>
+      <c r="P38">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2292,6 +2408,9 @@
       <c r="O39">
         <v>2</v>
       </c>
+      <c r="P39">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2341,6 +2460,9 @@
       <c r="O40">
         <v>1</v>
       </c>
+      <c r="P40">
+        <v>6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2390,6 +2512,9 @@
       <c r="O41">
         <v>3</v>
       </c>
+      <c r="P41">
+        <v>-99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2439,6 +2564,9 @@
       <c r="O42">
         <v>1</v>
       </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2488,6 +2616,9 @@
       <c r="O43">
         <v>1</v>
       </c>
+      <c r="P43">
+        <v>6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2537,6 +2668,9 @@
       <c r="O44">
         <v>1</v>
       </c>
+      <c r="P44">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2586,6 +2720,9 @@
       <c r="O45">
         <v>4</v>
       </c>
+      <c r="P45">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2635,6 +2772,9 @@
       <c r="O46">
         <v>2</v>
       </c>
+      <c r="P46">
+        <v>5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2684,6 +2824,9 @@
       <c r="O47">
         <v>1</v>
       </c>
+      <c r="P47">
+        <v>-98</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2733,6 +2876,9 @@
       <c r="O48">
         <v>5</v>
       </c>
+      <c r="P48">
+        <v>5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2782,6 +2928,9 @@
       <c r="O49">
         <v>5</v>
       </c>
+      <c r="P49">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2831,6 +2980,9 @@
       <c r="O50">
         <v>5</v>
       </c>
+      <c r="P50">
+        <v>7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2880,6 +3032,9 @@
       <c r="O51">
         <v>4</v>
       </c>
+      <c r="P51">
+        <v>7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2929,6 +3084,9 @@
       <c r="O52">
         <v>2</v>
       </c>
+      <c r="P52">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2978,6 +3136,9 @@
       <c r="O53">
         <v>3</v>
       </c>
+      <c r="P53">
+        <v>6</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3027,6 +3188,9 @@
       <c r="O54">
         <v>5</v>
       </c>
+      <c r="P54">
+        <v>6</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3076,6 +3240,9 @@
       <c r="O55">
         <v>1</v>
       </c>
+      <c r="P55">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3125,6 +3292,9 @@
       <c r="O56">
         <v>2</v>
       </c>
+      <c r="P56">
+        <v>7</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3174,6 +3344,9 @@
       <c r="O57">
         <v>1</v>
       </c>
+      <c r="P57">
+        <v>4</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3223,6 +3396,9 @@
       <c r="O58">
         <v>1</v>
       </c>
+      <c r="P58">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3272,6 +3448,9 @@
       <c r="O59">
         <v>4</v>
       </c>
+      <c r="P59">
+        <v>5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3321,6 +3500,9 @@
       <c r="O60">
         <v>3</v>
       </c>
+      <c r="P60">
+        <v>6</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3370,6 +3552,9 @@
       <c r="O61">
         <v>2</v>
       </c>
+      <c r="P61">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3419,6 +3604,9 @@
       <c r="O62">
         <v>2</v>
       </c>
+      <c r="P62">
+        <v>4</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3468,6 +3656,9 @@
       <c r="O63">
         <v>3</v>
       </c>
+      <c r="P63">
+        <v>9</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3517,6 +3708,9 @@
       <c r="O64">
         <v>1</v>
       </c>
+      <c r="P64">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3566,6 +3760,9 @@
       <c r="O65">
         <v>4</v>
       </c>
+      <c r="P65">
+        <v>4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3615,6 +3812,9 @@
       <c r="O66">
         <v>1</v>
       </c>
+      <c r="P66">
+        <v>4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3664,6 +3864,9 @@
       <c r="O67">
         <v>2</v>
       </c>
+      <c r="P67">
+        <v>4</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3713,6 +3916,9 @@
       <c r="O68">
         <v>1</v>
       </c>
+      <c r="P68">
+        <v>8</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3762,6 +3968,9 @@
       <c r="O69">
         <v>3</v>
       </c>
+      <c r="P69">
+        <v>6</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3811,6 +4020,9 @@
       <c r="O70">
         <v>5</v>
       </c>
+      <c r="P70">
+        <v>5</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3860,6 +4072,9 @@
       <c r="O71">
         <v>3</v>
       </c>
+      <c r="P71">
+        <v>5</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3909,6 +4124,9 @@
       <c r="O72">
         <v>2</v>
       </c>
+      <c r="P72">
+        <v>8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3958,6 +4176,9 @@
       <c r="O73">
         <v>1</v>
       </c>
+      <c r="P73">
+        <v>5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4007,6 +4228,9 @@
       <c r="O74">
         <v>4</v>
       </c>
+      <c r="P74">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4056,6 +4280,9 @@
       <c r="O75">
         <v>3</v>
       </c>
+      <c r="P75">
+        <v>5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4105,6 +4332,9 @@
       <c r="O76">
         <v>3</v>
       </c>
+      <c r="P76">
+        <v>9</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4154,6 +4384,9 @@
       <c r="O77">
         <v>1</v>
       </c>
+      <c r="P77">
+        <v>6</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4203,6 +4436,9 @@
       <c r="O78">
         <v>4</v>
       </c>
+      <c r="P78">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4252,6 +4488,9 @@
       <c r="O79">
         <v>2</v>
       </c>
+      <c r="P79">
+        <v>4</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4301,6 +4540,9 @@
       <c r="O80">
         <v>1</v>
       </c>
+      <c r="P80">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4350,6 +4592,9 @@
       <c r="O81">
         <v>1</v>
       </c>
+      <c r="P81">
+        <v>6</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4399,6 +4644,9 @@
       <c r="O82">
         <v>4</v>
       </c>
+      <c r="P82">
+        <v>8</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4448,6 +4696,9 @@
       <c r="O83">
         <v>5</v>
       </c>
+      <c r="P83">
+        <v>9</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4497,6 +4748,9 @@
       <c r="O84">
         <v>3</v>
       </c>
+      <c r="P84">
+        <v>8</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4546,6 +4800,9 @@
       <c r="O85">
         <v>4</v>
       </c>
+      <c r="P85">
+        <v>5</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4595,6 +4852,9 @@
       <c r="O86">
         <v>5</v>
       </c>
+      <c r="P86">
+        <v>-99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4644,6 +4904,9 @@
       <c r="O87">
         <v>1</v>
       </c>
+      <c r="P87">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4693,6 +4956,9 @@
       <c r="O88">
         <v>4</v>
       </c>
+      <c r="P88">
+        <v>6</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4742,6 +5008,9 @@
       <c r="O89">
         <v>3</v>
       </c>
+      <c r="P89">
+        <v>9</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4791,6 +5060,9 @@
       <c r="O90">
         <v>2</v>
       </c>
+      <c r="P90">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4840,6 +5112,9 @@
       <c r="O91">
         <v>3</v>
       </c>
+      <c r="P91">
+        <v>7</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4889,6 +5164,9 @@
       <c r="O92">
         <v>5</v>
       </c>
+      <c r="P92">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4938,6 +5216,9 @@
       <c r="O93">
         <v>4</v>
       </c>
+      <c r="P93">
+        <v>6</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4987,6 +5268,9 @@
       <c r="O94">
         <v>5</v>
       </c>
+      <c r="P94">
+        <v>7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5036,6 +5320,9 @@
       <c r="O95">
         <v>4</v>
       </c>
+      <c r="P95">
+        <v>7</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5085,6 +5372,9 @@
       <c r="O96">
         <v>5</v>
       </c>
+      <c r="P96">
+        <v>7</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5134,6 +5424,9 @@
       <c r="O97">
         <v>2</v>
       </c>
+      <c r="P97">
+        <v>7</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5183,6 +5476,9 @@
       <c r="O98">
         <v>4</v>
       </c>
+      <c r="P98">
+        <v>5</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5232,6 +5528,9 @@
       <c r="O99">
         <v>4</v>
       </c>
+      <c r="P99">
+        <v>10</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5281,6 +5580,9 @@
       <c r="O100">
         <v>4</v>
       </c>
+      <c r="P100">
+        <v>7</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5329,6 +5631,9 @@
       </c>
       <c r="O101">
         <v>5</v>
+      </c>
+      <c r="P101">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/community_excel.xlsx
+++ b/inst/extdata/community_excel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -430,11 +430,6 @@
           <t>Environment5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>JobSatisfaction</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -484,9 +479,6 @@
       <c r="O2">
         <v>4</v>
       </c>
-      <c r="P2">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,9 +528,6 @@
       <c r="O3">
         <v>4</v>
       </c>
-      <c r="P3">
-        <v>-98</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -588,9 +577,6 @@
       <c r="O4">
         <v>4</v>
       </c>
-      <c r="P4">
-        <v>5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,9 +626,6 @@
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="P5">
-        <v>7</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -692,9 +675,6 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="P6">
-        <v>4</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -744,9 +724,6 @@
       <c r="O7">
         <v>5</v>
       </c>
-      <c r="P7">
-        <v>4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -796,9 +773,6 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -848,9 +822,6 @@
       <c r="O9">
         <v>5</v>
       </c>
-      <c r="P9">
-        <v>9</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -900,9 +871,6 @@
       <c r="O10">
         <v>5</v>
       </c>
-      <c r="P10">
-        <v>6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -952,9 +920,6 @@
       <c r="O11">
         <v>1</v>
       </c>
-      <c r="P11">
-        <v>8</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1004,9 +969,6 @@
       <c r="O12">
         <v>3</v>
       </c>
-      <c r="P12">
-        <v>6</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1056,9 +1018,6 @@
       <c r="O13">
         <v>5</v>
       </c>
-      <c r="P13">
-        <v>4</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1108,9 +1067,6 @@
       <c r="O14">
         <v>3</v>
       </c>
-      <c r="P14">
-        <v>6</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1160,9 +1116,6 @@
       <c r="O15">
         <v>3</v>
       </c>
-      <c r="P15">
-        <v>8</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1212,9 +1165,6 @@
       <c r="O16">
         <v>4</v>
       </c>
-      <c r="P16">
-        <v>7</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1264,9 +1214,6 @@
       <c r="O17">
         <v>5</v>
       </c>
-      <c r="P17">
-        <v>6</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1316,9 +1263,6 @@
       <c r="O18">
         <v>5</v>
       </c>
-      <c r="P18">
-        <v>4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1368,9 +1312,6 @@
       <c r="O19">
         <v>2</v>
       </c>
-      <c r="P19">
-        <v>8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1420,9 +1361,6 @@
       <c r="O20">
         <v>3</v>
       </c>
-      <c r="P20">
-        <v>5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1472,9 +1410,6 @@
       <c r="O21">
         <v>1</v>
       </c>
-      <c r="P21">
-        <v>4</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1524,9 +1459,6 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22">
-        <v>-98</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1576,9 +1508,6 @@
       <c r="O23">
         <v>1</v>
       </c>
-      <c r="P23">
-        <v>5</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1628,9 +1557,6 @@
       <c r="O24">
         <v>1</v>
       </c>
-      <c r="P24">
-        <v>-99</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1680,9 +1606,6 @@
       <c r="O25">
         <v>3</v>
       </c>
-      <c r="P25">
-        <v>5</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1732,9 +1655,6 @@
       <c r="O26">
         <v>1</v>
       </c>
-      <c r="P26">
-        <v>10</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1784,9 +1704,6 @@
       <c r="O27">
         <v>5</v>
       </c>
-      <c r="P27">
-        <v>6</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1836,9 +1753,6 @@
       <c r="O28">
         <v>3</v>
       </c>
-      <c r="P28">
-        <v>7</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1888,9 +1802,6 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="P29">
-        <v>9</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1940,9 +1851,6 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="P30">
-        <v>5</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1992,9 +1900,6 @@
       <c r="O31">
         <v>4</v>
       </c>
-      <c r="P31">
-        <v>5</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2044,9 +1949,6 @@
       <c r="O32">
         <v>2</v>
       </c>
-      <c r="P32">
-        <v>3</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2096,9 +1998,6 @@
       <c r="O33">
         <v>5</v>
       </c>
-      <c r="P33">
-        <v>7</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2148,9 +2047,6 @@
       <c r="O34">
         <v>4</v>
       </c>
-      <c r="P34">
-        <v>6</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2200,9 +2096,6 @@
       <c r="O35">
         <v>3</v>
       </c>
-      <c r="P35">
-        <v>-99</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2252,9 +2145,6 @@
       <c r="O36">
         <v>3</v>
       </c>
-      <c r="P36">
-        <v>2</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2304,9 +2194,6 @@
       <c r="O37">
         <v>3</v>
       </c>
-      <c r="P37">
-        <v>5</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2356,9 +2243,6 @@
       <c r="O38">
         <v>5</v>
       </c>
-      <c r="P38">
-        <v>5</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2408,9 +2292,6 @@
       <c r="O39">
         <v>2</v>
       </c>
-      <c r="P39">
-        <v>4</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2460,9 +2341,6 @@
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="P40">
-        <v>6</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2512,9 +2390,6 @@
       <c r="O41">
         <v>3</v>
       </c>
-      <c r="P41">
-        <v>-99</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2564,9 +2439,6 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="P42">
-        <v>5</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2616,9 +2488,6 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="P43">
-        <v>6</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2668,9 +2537,6 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="P44">
-        <v>4</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2720,9 +2586,6 @@
       <c r="O45">
         <v>4</v>
       </c>
-      <c r="P45">
-        <v>3</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2772,9 +2635,6 @@
       <c r="O46">
         <v>2</v>
       </c>
-      <c r="P46">
-        <v>5</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2824,9 +2684,6 @@
       <c r="O47">
         <v>1</v>
       </c>
-      <c r="P47">
-        <v>-98</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2876,9 +2733,6 @@
       <c r="O48">
         <v>5</v>
       </c>
-      <c r="P48">
-        <v>5</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2928,9 +2782,6 @@
       <c r="O49">
         <v>5</v>
       </c>
-      <c r="P49">
-        <v>3</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2980,9 +2831,6 @@
       <c r="O50">
         <v>5</v>
       </c>
-      <c r="P50">
-        <v>7</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3032,9 +2880,6 @@
       <c r="O51">
         <v>4</v>
       </c>
-      <c r="P51">
-        <v>7</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3084,9 +2929,6 @@
       <c r="O52">
         <v>2</v>
       </c>
-      <c r="P52">
-        <v>3</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3136,9 +2978,6 @@
       <c r="O53">
         <v>3</v>
       </c>
-      <c r="P53">
-        <v>6</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3188,9 +3027,6 @@
       <c r="O54">
         <v>5</v>
       </c>
-      <c r="P54">
-        <v>6</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3240,9 +3076,6 @@
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="P55">
-        <v>8</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3292,9 +3125,6 @@
       <c r="O56">
         <v>2</v>
       </c>
-      <c r="P56">
-        <v>7</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3344,9 +3174,6 @@
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="P57">
-        <v>4</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3396,9 +3223,6 @@
       <c r="O58">
         <v>1</v>
       </c>
-      <c r="P58">
-        <v>7</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3448,9 +3272,6 @@
       <c r="O59">
         <v>4</v>
       </c>
-      <c r="P59">
-        <v>5</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3500,9 +3321,6 @@
       <c r="O60">
         <v>3</v>
       </c>
-      <c r="P60">
-        <v>6</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3552,9 +3370,6 @@
       <c r="O61">
         <v>2</v>
       </c>
-      <c r="P61">
-        <v>5</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3604,9 +3419,6 @@
       <c r="O62">
         <v>2</v>
       </c>
-      <c r="P62">
-        <v>4</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3656,9 +3468,6 @@
       <c r="O63">
         <v>3</v>
       </c>
-      <c r="P63">
-        <v>9</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3708,9 +3517,6 @@
       <c r="O64">
         <v>1</v>
       </c>
-      <c r="P64">
-        <v>8</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3760,9 +3566,6 @@
       <c r="O65">
         <v>4</v>
       </c>
-      <c r="P65">
-        <v>4</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3812,9 +3615,6 @@
       <c r="O66">
         <v>1</v>
       </c>
-      <c r="P66">
-        <v>4</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3864,9 +3664,6 @@
       <c r="O67">
         <v>2</v>
       </c>
-      <c r="P67">
-        <v>4</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3916,9 +3713,6 @@
       <c r="O68">
         <v>1</v>
       </c>
-      <c r="P68">
-        <v>8</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3968,9 +3762,6 @@
       <c r="O69">
         <v>3</v>
       </c>
-      <c r="P69">
-        <v>6</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4020,9 +3811,6 @@
       <c r="O70">
         <v>5</v>
       </c>
-      <c r="P70">
-        <v>5</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4072,9 +3860,6 @@
       <c r="O71">
         <v>3</v>
       </c>
-      <c r="P71">
-        <v>5</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4124,9 +3909,6 @@
       <c r="O72">
         <v>2</v>
       </c>
-      <c r="P72">
-        <v>8</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4176,9 +3958,6 @@
       <c r="O73">
         <v>1</v>
       </c>
-      <c r="P73">
-        <v>5</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4228,9 +4007,6 @@
       <c r="O74">
         <v>4</v>
       </c>
-      <c r="P74">
-        <v>3</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4280,9 +4056,6 @@
       <c r="O75">
         <v>3</v>
       </c>
-      <c r="P75">
-        <v>5</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4332,9 +4105,6 @@
       <c r="O76">
         <v>3</v>
       </c>
-      <c r="P76">
-        <v>9</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4384,9 +4154,6 @@
       <c r="O77">
         <v>1</v>
       </c>
-      <c r="P77">
-        <v>6</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4436,9 +4203,6 @@
       <c r="O78">
         <v>4</v>
       </c>
-      <c r="P78">
-        <v>8</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4488,9 +4252,6 @@
       <c r="O79">
         <v>2</v>
       </c>
-      <c r="P79">
-        <v>4</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4540,9 +4301,6 @@
       <c r="O80">
         <v>1</v>
       </c>
-      <c r="P80">
-        <v>2</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4592,9 +4350,6 @@
       <c r="O81">
         <v>1</v>
       </c>
-      <c r="P81">
-        <v>6</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4644,9 +4399,6 @@
       <c r="O82">
         <v>4</v>
       </c>
-      <c r="P82">
-        <v>8</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4696,9 +4448,6 @@
       <c r="O83">
         <v>5</v>
       </c>
-      <c r="P83">
-        <v>9</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4748,9 +4497,6 @@
       <c r="O84">
         <v>3</v>
       </c>
-      <c r="P84">
-        <v>8</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4800,9 +4546,6 @@
       <c r="O85">
         <v>4</v>
       </c>
-      <c r="P85">
-        <v>5</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4852,9 +4595,6 @@
       <c r="O86">
         <v>5</v>
       </c>
-      <c r="P86">
-        <v>-99</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4904,9 +4644,6 @@
       <c r="O87">
         <v>1</v>
       </c>
-      <c r="P87">
-        <v>7</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4956,9 +4693,6 @@
       <c r="O88">
         <v>4</v>
       </c>
-      <c r="P88">
-        <v>6</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5008,9 +4742,6 @@
       <c r="O89">
         <v>3</v>
       </c>
-      <c r="P89">
-        <v>9</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5060,9 +4791,6 @@
       <c r="O90">
         <v>2</v>
       </c>
-      <c r="P90">
-        <v>7</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5112,9 +4840,6 @@
       <c r="O91">
         <v>3</v>
       </c>
-      <c r="P91">
-        <v>7</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5164,9 +4889,6 @@
       <c r="O92">
         <v>5</v>
       </c>
-      <c r="P92">
-        <v>3</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5216,9 +4938,6 @@
       <c r="O93">
         <v>4</v>
       </c>
-      <c r="P93">
-        <v>6</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5268,9 +4987,6 @@
       <c r="O94">
         <v>5</v>
       </c>
-      <c r="P94">
-        <v>7</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5320,9 +5036,6 @@
       <c r="O95">
         <v>4</v>
       </c>
-      <c r="P95">
-        <v>7</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5372,9 +5085,6 @@
       <c r="O96">
         <v>5</v>
       </c>
-      <c r="P96">
-        <v>7</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5424,9 +5134,6 @@
       <c r="O97">
         <v>2</v>
       </c>
-      <c r="P97">
-        <v>7</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5476,9 +5183,6 @@
       <c r="O98">
         <v>4</v>
       </c>
-      <c r="P98">
-        <v>5</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5528,9 +5232,6 @@
       <c r="O99">
         <v>4</v>
       </c>
-      <c r="P99">
-        <v>10</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5580,9 +5281,6 @@
       <c r="O100">
         <v>4</v>
       </c>
-      <c r="P100">
-        <v>7</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5631,9 +5329,6 @@
       </c>
       <c r="O101">
         <v>5</v>
-      </c>
-      <c r="P101">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/community_excel.xlsx
+++ b/inst/extdata/community_excel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,46 +438,46 @@
         </is>
       </c>
       <c r="B2">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>33</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -487,46 +487,46 @@
         </is>
       </c>
       <c r="B3">
-        <v>-99</v>
+        <v>43000</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -536,37 +536,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>64000</v>
+        <v>28000</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>43</v>
       </c>
       <c r="E4">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -585,43 +585,43 @@
         </is>
       </c>
       <c r="B5">
-        <v>88000</v>
+        <v>46000</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>43</v>
       </c>
       <c r="E5">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>14000</v>
+        <v>46000</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -652,28 +652,28 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>22000</v>
+        <v>-99</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>48</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -701,28 +701,28 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>3</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7">
         <v>3</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -741,10 +741,10 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -753,25 +753,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <v>3</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>47000</v>
+        <v>65000</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>46</v>
       </c>
       <c r="E9">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -802,25 +802,25 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -830,46 +830,46 @@
         </is>
       </c>
       <c r="B10">
-        <v>48000</v>
+        <v>33000</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>35</v>
       </c>
       <c r="E10">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -879,46 +879,46 @@
         </is>
       </c>
       <c r="B11">
-        <v>45000</v>
+        <v>73000</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>-99</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11">
         <v>2</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -928,19 +928,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>46000</v>
+        <v>17000</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -949,25 +949,25 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -977,31 +977,31 @@
         </is>
       </c>
       <c r="B13">
-        <v>38000</v>
+        <v>62000</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>41</v>
       </c>
       <c r="E13">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>3</v>
@@ -1010,13 +1010,13 @@
         <v>4</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>-99</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>-99</v>
+        <v>30000</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>33</v>
       </c>
       <c r="E14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1044,19 +1044,19 @@
         <v>2</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -1065,7 +1065,7 @@
         <v>3</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15">
         <v>24</v>
       </c>
       <c r="E15">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1096,25 +1096,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>4</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="B16">
-        <v>18000</v>
+        <v>39000</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>35</v>
       </c>
       <c r="E16">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>4</v>
@@ -1173,46 +1173,46 @@
         </is>
       </c>
       <c r="B17">
-        <v>56000</v>
+        <v>34000</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="D17">
         <v>32</v>
       </c>
       <c r="E17">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1225,43 +1225,43 @@
         <v>44000</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>41</v>
       </c>
       <c r="E18">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>76000</v>
+        <v>75000</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -1280,37 +1280,37 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>2</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>3</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1323,13 +1323,13 @@
         <v>14000</v>
       </c>
       <c r="C20">
-        <v>-98</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>24</v>
       </c>
       <c r="E20">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1338,28 +1338,28 @@
         <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20">
         <v>3</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1369,16 +1369,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>20000</v>
+        <v>69000</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>66</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1390,25 +1390,25 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>-98</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1418,16 +1418,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>80000</v>
+        <v>58000</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <v>62</v>
       </c>
       <c r="E22">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1439,25 +1439,25 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1467,46 +1467,46 @@
         </is>
       </c>
       <c r="B23">
-        <v>14000</v>
+        <v>65000</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>28</v>
       </c>
       <c r="E23">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1516,46 +1516,46 @@
         </is>
       </c>
       <c r="B24">
-        <v>66000</v>
+        <v>75000</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24">
         <v>36</v>
       </c>
       <c r="E24">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J24">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L24">
         <v>3</v>
       </c>
       <c r="M24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1565,43 +1565,43 @@
         </is>
       </c>
       <c r="B25">
-        <v>54000</v>
+        <v>28000</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>35</v>
       </c>
       <c r="E25">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>4</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>-98</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>3</v>
@@ -1614,46 +1614,46 @@
         </is>
       </c>
       <c r="B26">
-        <v>58000</v>
+        <v>38000</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>54</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1663,46 +1663,46 @@
         </is>
       </c>
       <c r="B27">
-        <v>62000</v>
+        <v>33000</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>45</v>
       </c>
       <c r="E27">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O27">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1715,43 +1715,43 @@
         <v>-98</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>49</v>
       </c>
       <c r="E28">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1761,43 +1761,43 @@
         </is>
       </c>
       <c r="B29">
-        <v>46000</v>
+        <v>38000</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>34</v>
       </c>
       <c r="E29">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29">
         <v>3</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -1810,46 +1810,46 @@
         </is>
       </c>
       <c r="B30">
-        <v>14000</v>
+        <v>58000</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30">
         <v>36</v>
       </c>
       <c r="E30">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>-99</v>
+        <v>-98</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>-99</v>
+        <v>4</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>-98</v>
+        <v>38000</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1880,25 +1880,25 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31">
         <v>4</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1908,46 +1908,46 @@
         </is>
       </c>
       <c r="B32">
-        <v>14000</v>
+        <v>-98</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>31</v>
       </c>
       <c r="E32">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1957,19 +1957,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>65000</v>
+        <v>36000</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>54</v>
       </c>
       <c r="E33">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1978,25 +1978,25 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2006,19 +2006,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>91000</v>
+        <v>63000</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>69</v>
       </c>
       <c r="E34">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34">
         <v>2</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N34">
         <v>2</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>91000</v>
+        <v>47000</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -2064,37 +2064,37 @@
         <v>44</v>
       </c>
       <c r="E35">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2104,16 +2104,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>56000</v>
+        <v>35000</v>
       </c>
       <c r="C36">
-        <v>-98</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>33</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2122,28 +2122,28 @@
         <v>2</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>-99</v>
       </c>
       <c r="I36">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2153,46 +2153,46 @@
         </is>
       </c>
       <c r="B37">
-        <v>39000</v>
+        <v>34000</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <v>37</v>
       </c>
       <c r="E37">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
       <c r="H37">
-        <v>-99</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>49000</v>
+        <v>58000</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -2211,7 +2211,7 @@
         <v>29</v>
       </c>
       <c r="E38">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2223,25 +2223,25 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38">
-        <v>-98</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>17000</v>
+        <v>45000</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -2260,37 +2260,37 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="J39">
         <v>4</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="L39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="N39">
         <v>3</v>
       </c>
       <c r="O39">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2300,16 +2300,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>76000</v>
+        <v>27000</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="D40">
         <v>40</v>
       </c>
       <c r="E40">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2318,28 +2318,28 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40">
         <v>3</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40">
         <v>4</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2349,46 +2349,46 @@
         </is>
       </c>
       <c r="B41">
-        <v>44000</v>
+        <v>65000</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>35</v>
       </c>
       <c r="E41">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41">
-        <v>-98</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2398,40 +2398,40 @@
         </is>
       </c>
       <c r="B42">
-        <v>-99</v>
+        <v>53000</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>26</v>
       </c>
       <c r="E42">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>-98</v>
       </c>
       <c r="N42">
         <v>3</v>
@@ -2447,46 +2447,46 @@
         </is>
       </c>
       <c r="B43">
-        <v>40000</v>
+        <v>70000</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>24</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M43">
-        <v>-99</v>
+        <v>4</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2496,46 +2496,46 @@
         </is>
       </c>
       <c r="B44">
-        <v>39000</v>
+        <v>-98</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>50</v>
       </c>
       <c r="E44">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44">
         <v>2</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>25000</v>
+        <v>44000</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>32</v>
       </c>
       <c r="E45">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2566,25 +2566,25 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2594,43 +2594,43 @@
         </is>
       </c>
       <c r="B46">
-        <v>46000</v>
+        <v>36000</v>
       </c>
       <c r="C46">
-        <v>-99</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <v>29</v>
       </c>
       <c r="E46">
+        <v>47</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
         <v>36</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>2</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>18</v>
-      </c>
       <c r="J46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>2</v>
@@ -2643,46 +2643,46 @@
         </is>
       </c>
       <c r="B47">
-        <v>56000</v>
+        <v>62000</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>41</v>
       </c>
       <c r="E47">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47">
         <v>3</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2692,19 +2692,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>38000</v>
+        <v>62000</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <v>34</v>
       </c>
       <c r="E48">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2713,25 +2713,25 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -2741,46 +2741,46 @@
         </is>
       </c>
       <c r="B49">
-        <v>55000</v>
+        <v>43000</v>
       </c>
       <c r="C49">
-        <v>-99</v>
+        <v>3</v>
       </c>
       <c r="D49">
         <v>49</v>
       </c>
       <c r="E49">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49">
-        <v>-98</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O49">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="B50">
-        <v>68000</v>
+        <v>56000</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>39</v>
       </c>
       <c r="E50">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2811,25 +2811,25 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
         <v>1</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50">
         <v>5</v>
       </c>
       <c r="O50">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -2839,46 +2839,46 @@
         </is>
       </c>
       <c r="B51">
-        <v>61000</v>
+        <v>47000</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>33</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2888,40 +2888,40 @@
         </is>
       </c>
       <c r="B52">
-        <v>58000</v>
+        <v>53000</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>61</v>
       </c>
       <c r="E52">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J52">
         <v>3</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>29000</v>
+        <v>25000</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -2946,10 +2946,10 @@
         <v>31</v>
       </c>
       <c r="E53">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2958,25 +2958,25 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53">
         <v>2</v>
       </c>
       <c r="O53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>14000</v>
+        <v>74000</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>27</v>
@@ -3001,13 +3001,13 @@
         <v>1</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>-99</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J54">
         <v>3</v>
@@ -3016,13 +3016,13 @@
         <v>3</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M54">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O54">
         <v>5</v>
@@ -3035,46 +3035,46 @@
         </is>
       </c>
       <c r="B55">
-        <v>60000</v>
+        <v>72000</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>44</v>
       </c>
       <c r="E55">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>-99</v>
       </c>
       <c r="I55">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J55">
         <v>3</v>
       </c>
       <c r="K55">
-        <v>-99</v>
+        <v>5</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>-99</v>
+        <v>5</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3084,19 +3084,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>65000</v>
+        <v>64000</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="D56">
         <v>45</v>
       </c>
       <c r="E56">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3105,25 +3105,25 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>-98</v>
       </c>
       <c r="L56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="N56">
         <v>3</v>
       </c>
       <c r="O56">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3133,46 +3133,46 @@
         </is>
       </c>
       <c r="B57">
-        <v>41000</v>
+        <v>15000</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>22</v>
       </c>
       <c r="E57">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <v>2</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M57">
         <v>3</v>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O57">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3182,31 +3182,31 @@
         </is>
       </c>
       <c r="B58">
-        <v>46000</v>
+        <v>57000</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>26</v>
       </c>
       <c r="E58">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>2</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="I58">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K58">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>4</v>
       </c>
       <c r="O58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="B59">
-        <v>43000</v>
+        <v>45000</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>18</v>
       </c>
       <c r="E59">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3252,25 +3252,25 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="J59">
         <v>3</v>
       </c>
       <c r="K59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M59">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>31000</v>
+        <v>93000</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>32</v>
       </c>
       <c r="E60">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J60">
         <v>3</v>
@@ -3310,16 +3310,16 @@
         <v>3</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N60">
         <v>2</v>
       </c>
       <c r="O60">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>26000</v>
+        <v>49000</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -3338,7 +3338,7 @@
         <v>46</v>
       </c>
       <c r="E61">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3347,10 +3347,10 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J61">
         <v>4</v>
@@ -3359,10 +3359,10 @@
         <v>2</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61">
         <v>3</v>
@@ -3378,46 +3378,46 @@
         </is>
       </c>
       <c r="B62">
-        <v>20000</v>
+        <v>-99</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>56</v>
       </c>
       <c r="E62">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N62">
         <v>4</v>
       </c>
       <c r="O62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>82000</v>
+        <v>64000</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <v>44</v>
@@ -3445,28 +3445,28 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N63">
         <v>3</v>
       </c>
       <c r="O63">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -3476,16 +3476,16 @@
         </is>
       </c>
       <c r="B64">
-        <v>39000</v>
+        <v>30000</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>18</v>
       </c>
       <c r="E64">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3494,28 +3494,28 @@
         <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J64">
         <v>3</v>
       </c>
       <c r="K64">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N64">
         <v>2</v>
       </c>
       <c r="O64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3525,16 +3525,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>24</v>
       </c>
       <c r="E65">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3543,28 +3543,28 @@
         <v>2</v>
       </c>
       <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>23</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65">
         <v>-99</v>
       </c>
-      <c r="I65">
-        <v>47</v>
-      </c>
-      <c r="J65">
-        <v>2</v>
-      </c>
-      <c r="K65">
-        <v>-98</v>
-      </c>
       <c r="L65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M65">
         <v>-99</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O65">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -3583,37 +3583,37 @@
         <v>40</v>
       </c>
       <c r="E66">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>2</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J66">
         <v>3</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3623,46 +3623,46 @@
         </is>
       </c>
       <c r="B67">
-        <v>28000</v>
+        <v>46000</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>63</v>
       </c>
       <c r="E67">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>2</v>
+        <v>-98</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O67">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>70000</v>
+        <v>68000</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -3681,7 +3681,7 @@
         <v>47</v>
       </c>
       <c r="E68">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -3690,25 +3690,25 @@
         <v>2</v>
       </c>
       <c r="H68">
-        <v>-99</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J68">
         <v>4</v>
       </c>
       <c r="K68">
-        <v>-99</v>
+        <v>3</v>
       </c>
       <c r="L68">
         <v>2</v>
       </c>
       <c r="M68">
-        <v>-99</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68">
         <v>1</v>
@@ -3721,46 +3721,46 @@
         </is>
       </c>
       <c r="B69">
-        <v>37000</v>
+        <v>48000</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>-99</v>
       </c>
       <c r="D69">
         <v>46</v>
       </c>
       <c r="E69">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69">
-        <v>-99</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B70">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>36</v>
       </c>
       <c r="E70">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3788,28 +3788,28 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J70">
         <v>1</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L70">
         <v>2</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O70">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>69000</v>
+        <v>49000</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -3828,31 +3828,31 @@
         <v>53</v>
       </c>
       <c r="E71">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71">
         <v>3</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>-99</v>
       </c>
       <c r="N71">
         <v>2</v>
@@ -3868,16 +3868,16 @@
         </is>
       </c>
       <c r="B72">
-        <v>43000</v>
+        <v>35000</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72">
         <v>48</v>
       </c>
       <c r="E72">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -3886,28 +3886,28 @@
         <v>2</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72">
-        <v>-99</v>
+        <v>3</v>
       </c>
       <c r="L72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -3917,46 +3917,46 @@
         </is>
       </c>
       <c r="B73">
-        <v>48000</v>
+        <v>-99</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <v>47</v>
       </c>
       <c r="E73">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="B74">
-        <v>75000</v>
+        <v>20000</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>39</v>
       </c>
       <c r="E74">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3987,25 +3987,25 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4015,16 +4015,16 @@
         </is>
       </c>
       <c r="B75">
-        <v>57000</v>
+        <v>65000</v>
       </c>
       <c r="C75">
-        <v>-99</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>36</v>
       </c>
       <c r="E75">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -4033,28 +4033,28 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>-98</v>
+        <v>-99</v>
       </c>
       <c r="L75">
         <v>3</v>
       </c>
       <c r="M75">
-        <v>-98</v>
+        <v>-99</v>
       </c>
       <c r="N75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -4064,46 +4064,46 @@
         </is>
       </c>
       <c r="B76">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>41</v>
       </c>
       <c r="E76">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J76">
         <v>3</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L76">
         <v>3</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>36000</v>
+        <v>48000</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -4122,37 +4122,37 @@
         <v>40</v>
       </c>
       <c r="E77">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>-99</v>
       </c>
       <c r="I77">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77">
         <v>3</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>68000</v>
+        <v>54000</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>48</v>
@@ -4177,31 +4177,31 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>5</v>
+        <v>-98</v>
       </c>
       <c r="L78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4211,46 +4211,46 @@
         </is>
       </c>
       <c r="B79">
-        <v>28000</v>
+        <v>76000</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79">
         <v>60</v>
       </c>
       <c r="E79">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K79">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="L79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4260,46 +4260,46 @@
         </is>
       </c>
       <c r="B80">
-        <v>23000</v>
+        <v>75000</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>54</v>
       </c>
       <c r="E80">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80">
-        <v>-99</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80">
-        <v>-99</v>
+        <v>-98</v>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="B81">
-        <v>48000</v>
+        <v>52000</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>-99</v>
       </c>
       <c r="D81">
         <v>30</v>
       </c>
       <c r="E81">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4327,28 +4327,28 @@
         <v>2</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O81">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -4358,16 +4358,16 @@
         </is>
       </c>
       <c r="B82">
-        <v>48000</v>
+        <v>54000</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82">
         <v>51</v>
       </c>
       <c r="E82">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -4376,28 +4376,28 @@
         <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -4407,46 +4407,46 @@
         </is>
       </c>
       <c r="B83">
-        <v>72000</v>
+        <v>55000</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>41</v>
       </c>
       <c r="E83">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O83">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>82000</v>
+        <v>85000</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -4465,19 +4465,19 @@
         <v>52</v>
       </c>
       <c r="E84">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="J84">
         <v>4</v>
@@ -4486,13 +4486,13 @@
         <v>3</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N84">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O84">
         <v>3</v>
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="B85">
-        <v>-98</v>
+        <v>63000</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>32</v>
       </c>
       <c r="E85">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4523,28 +4523,28 @@
         <v>2</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J85">
         <v>2</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M85">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -4554,16 +4554,16 @@
         </is>
       </c>
       <c r="B86">
-        <v>60000</v>
+        <v>31000</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <v>24</v>
       </c>
       <c r="E86">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4575,25 +4575,25 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O86">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4603,40 +4603,40 @@
         </is>
       </c>
       <c r="B87">
-        <v>51000</v>
+        <v>33000</v>
       </c>
       <c r="C87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>71</v>
       </c>
       <c r="E87">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87">
-        <v>-99</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="J87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L87">
         <v>3</v>
       </c>
       <c r="M87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N87">
         <v>3</v>
@@ -4655,28 +4655,28 @@
         <v>28000</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D88">
         <v>41</v>
       </c>
       <c r="E88">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -4685,13 +4685,13 @@
         <v>1</v>
       </c>
       <c r="M88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N88">
         <v>4</v>
       </c>
       <c r="O88">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -4701,46 +4701,46 @@
         </is>
       </c>
       <c r="B89">
-        <v>56000</v>
+        <v>72000</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89">
         <v>58</v>
       </c>
       <c r="E89">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K89">
         <v>2</v>
       </c>
       <c r="L89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O89">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -4750,19 +4750,19 @@
         </is>
       </c>
       <c r="B90">
-        <v>14000</v>
+        <v>80000</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>42</v>
       </c>
       <c r="E90">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -4771,25 +4771,25 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90">
         <v>3</v>
       </c>
       <c r="N90">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O90">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -4799,28 +4799,28 @@
         </is>
       </c>
       <c r="B91">
-        <v>63000</v>
+        <v>54000</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>40</v>
       </c>
       <c r="E91">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>0</v>
       </c>
       <c r="I91">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J91">
         <v>2</v>
@@ -4832,13 +4832,13 @@
         <v>5</v>
       </c>
       <c r="M91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91">
         <v>1</v>
       </c>
       <c r="O91">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>62000</v>
+        <v>65000</v>
       </c>
       <c r="C92">
         <v>4</v>
@@ -4857,7 +4857,7 @@
         <v>36</v>
       </c>
       <c r="E92">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K92">
         <v>4</v>
@@ -4881,7 +4881,7 @@
         <v>3</v>
       </c>
       <c r="M92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N92">
         <v>5</v>
@@ -4897,46 +4897,46 @@
         </is>
       </c>
       <c r="B93">
-        <v>49000</v>
+        <v>52000</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93">
         <v>45</v>
       </c>
       <c r="E93">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O93">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4946,16 +4946,16 @@
         </is>
       </c>
       <c r="B94">
-        <v>34000</v>
+        <v>52000</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94">
         <v>44</v>
       </c>
       <c r="E94">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4964,13 +4964,13 @@
         <v>2</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K94">
         <v>4</v>
@@ -4979,13 +4979,13 @@
         <v>2</v>
       </c>
       <c r="M94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N94">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O94">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -4995,46 +4995,46 @@
         </is>
       </c>
       <c r="B95">
-        <v>54000</v>
+        <v>46000</v>
       </c>
       <c r="C95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95">
         <v>53</v>
       </c>
       <c r="E95">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="I95">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M95">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N95">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -5044,46 +5044,46 @@
         </is>
       </c>
       <c r="B96">
-        <v>58000</v>
+        <v>63000</v>
       </c>
       <c r="C96">
-        <v>-98</v>
+        <v>3</v>
       </c>
       <c r="D96">
         <v>46</v>
       </c>
       <c r="E96">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L96">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M96">
         <v>5</v>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O96">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>77000</v>
+        <v>43000</v>
       </c>
       <c r="C97">
         <v>4</v>
@@ -5102,37 +5102,37 @@
         <v>35</v>
       </c>
       <c r="E97">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J97">
         <v>2</v>
       </c>
       <c r="K97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O97">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -5142,16 +5142,16 @@
         </is>
       </c>
       <c r="B98">
-        <v>67000</v>
+        <v>60000</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>64</v>
       </c>
       <c r="E98">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -5163,25 +5163,25 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J98">
         <v>4</v>
       </c>
       <c r="K98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L98">
         <v>3</v>
       </c>
       <c r="M98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O98">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5191,31 +5191,31 @@
         </is>
       </c>
       <c r="B99">
-        <v>59000</v>
+        <v>77000</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D99">
         <v>51</v>
       </c>
       <c r="E99">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K99">
         <v>4</v>
@@ -5224,13 +5224,13 @@
         <v>2</v>
       </c>
       <c r="M99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -5240,19 +5240,19 @@
         </is>
       </c>
       <c r="B100">
-        <v>69000</v>
+        <v>58000</v>
       </c>
       <c r="C100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D100">
         <v>46</v>
       </c>
       <c r="E100">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -5261,16 +5261,16 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J100">
         <v>1</v>
       </c>
       <c r="K100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M100">
         <v>4</v>
@@ -5279,7 +5279,7 @@
         <v>4</v>
       </c>
       <c r="O100">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -5289,16 +5289,16 @@
         </is>
       </c>
       <c r="B101">
-        <v>51000</v>
+        <v>29000</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>18</v>
       </c>
       <c r="E101">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -5310,25 +5310,172 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K101">
         <v>4</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101">
-        <v>5</v>
+        <v>-98</v>
       </c>
       <c r="N101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>R101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>46000</v>
+      </c>
+      <c r="C102">
+        <v>-98</v>
+      </c>
+      <c r="D102">
+        <v>29</v>
+      </c>
+      <c r="E102">
+        <v>52</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>5</v>
+      </c>
+      <c r="J102">
+        <v>3</v>
+      </c>
+      <c r="K102">
+        <v>5</v>
+      </c>
+      <c r="L102">
+        <v>3</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+      <c r="N102">
+        <v>4</v>
+      </c>
+      <c r="O102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>R102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>67000</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
+      </c>
+      <c r="D103">
+        <v>52</v>
+      </c>
+      <c r="E103">
+        <v>69</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>39</v>
+      </c>
+      <c r="J103">
+        <v>3</v>
+      </c>
+      <c r="K103">
+        <v>5</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>4</v>
+      </c>
+      <c r="N103">
+        <v>5</v>
+      </c>
+      <c r="O103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>75000</v>
+      </c>
+      <c r="C104">
+        <v>3</v>
+      </c>
+      <c r="D104">
+        <v>40</v>
+      </c>
+      <c r="E104">
+        <v>68</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>33</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>3</v>
+      </c>
+      <c r="M104">
+        <v>2</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
